--- a/WK_Model.xlsx
+++ b/WK_Model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Technology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79F4454D-A3DB-4FEA-A716-98838974B8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B6E2F84-443D-4BCC-A415-0B1F2BF0D80B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,6 @@
     <sheet name="Table Formatting" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -6001,6 +6000,15 @@
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -6036,15 +6044,6 @@
     </xf>
     <xf numFmtId="10" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -13688,23 +13687,23 @@
       </c>
     </row>
     <row r="48" spans="1:21" ht="14.25" customHeight="1">
-      <c r="B48" s="103" t="s">
+      <c r="B48" s="91" t="s">
         <v>1474</v>
       </c>
-      <c r="C48" s="103"/>
-      <c r="D48" s="103"/>
-      <c r="E48" s="103"/>
-      <c r="F48" s="103"/>
-      <c r="G48" s="103"/>
-      <c r="H48" s="103"/>
-      <c r="I48" s="103"/>
-      <c r="J48" s="103"/>
-      <c r="K48" s="103"/>
-      <c r="L48" s="103"/>
-      <c r="M48" s="103"/>
-      <c r="N48" s="103"/>
-      <c r="O48" s="103"/>
-      <c r="P48" s="103"/>
+      <c r="C48" s="91"/>
+      <c r="D48" s="91"/>
+      <c r="E48" s="91"/>
+      <c r="F48" s="91"/>
+      <c r="G48" s="91"/>
+      <c r="H48" s="91"/>
+      <c r="I48" s="91"/>
+      <c r="J48" s="91"/>
+      <c r="K48" s="91"/>
+      <c r="L48" s="91"/>
+      <c r="M48" s="91"/>
+      <c r="N48" s="91"/>
+      <c r="O48" s="91"/>
+      <c r="P48" s="91"/>
       <c r="Q48" s="45"/>
       <c r="R48" s="60"/>
       <c r="S48" s="60"/>
@@ -13712,21 +13711,21 @@
       <c r="U48" s="60"/>
     </row>
     <row r="49" spans="1:21">
-      <c r="B49" s="103"/>
-      <c r="C49" s="103"/>
-      <c r="D49" s="103"/>
-      <c r="E49" s="103"/>
-      <c r="F49" s="103"/>
-      <c r="G49" s="103"/>
-      <c r="H49" s="103"/>
-      <c r="I49" s="103"/>
-      <c r="J49" s="103"/>
-      <c r="K49" s="103"/>
-      <c r="L49" s="103"/>
-      <c r="M49" s="103"/>
-      <c r="N49" s="103"/>
-      <c r="O49" s="103"/>
-      <c r="P49" s="103"/>
+      <c r="B49" s="91"/>
+      <c r="C49" s="91"/>
+      <c r="D49" s="91"/>
+      <c r="E49" s="91"/>
+      <c r="F49" s="91"/>
+      <c r="G49" s="91"/>
+      <c r="H49" s="91"/>
+      <c r="I49" s="91"/>
+      <c r="J49" s="91"/>
+      <c r="K49" s="91"/>
+      <c r="L49" s="91"/>
+      <c r="M49" s="91"/>
+      <c r="N49" s="91"/>
+      <c r="O49" s="91"/>
+      <c r="P49" s="91"/>
       <c r="Q49" s="45"/>
       <c r="R49" s="60"/>
       <c r="S49" s="60"/>
@@ -13909,131 +13908,131 @@
       </c>
     </row>
     <row r="87" spans="3:27" ht="14.25" customHeight="1">
-      <c r="E87" s="103" t="s">
+      <c r="E87" s="91" t="s">
         <v>1572</v>
       </c>
-      <c r="F87" s="103"/>
-      <c r="G87" s="103"/>
-      <c r="H87" s="103"/>
-      <c r="I87" s="103"/>
-      <c r="J87" s="103"/>
-      <c r="K87" s="103"/>
-      <c r="L87" s="103"/>
-      <c r="M87" s="103"/>
-      <c r="N87" s="103"/>
-      <c r="O87" s="103"/>
-      <c r="P87" s="103"/>
-      <c r="Q87" s="103"/>
-      <c r="R87" s="103"/>
-      <c r="S87" s="103"/>
-      <c r="T87" s="103"/>
-      <c r="U87" s="103"/>
-      <c r="V87" s="103"/>
-      <c r="W87" s="103"/>
-      <c r="X87" s="103"/>
-      <c r="Y87" s="103"/>
-      <c r="Z87" s="103"/>
-      <c r="AA87" s="103"/>
+      <c r="F87" s="91"/>
+      <c r="G87" s="91"/>
+      <c r="H87" s="91"/>
+      <c r="I87" s="91"/>
+      <c r="J87" s="91"/>
+      <c r="K87" s="91"/>
+      <c r="L87" s="91"/>
+      <c r="M87" s="91"/>
+      <c r="N87" s="91"/>
+      <c r="O87" s="91"/>
+      <c r="P87" s="91"/>
+      <c r="Q87" s="91"/>
+      <c r="R87" s="91"/>
+      <c r="S87" s="91"/>
+      <c r="T87" s="91"/>
+      <c r="U87" s="91"/>
+      <c r="V87" s="91"/>
+      <c r="W87" s="91"/>
+      <c r="X87" s="91"/>
+      <c r="Y87" s="91"/>
+      <c r="Z87" s="91"/>
+      <c r="AA87" s="91"/>
     </row>
     <row r="88" spans="3:27">
-      <c r="E88" s="103"/>
-      <c r="F88" s="103"/>
-      <c r="G88" s="103"/>
-      <c r="H88" s="103"/>
-      <c r="I88" s="103"/>
-      <c r="J88" s="103"/>
-      <c r="K88" s="103"/>
-      <c r="L88" s="103"/>
-      <c r="M88" s="103"/>
-      <c r="N88" s="103"/>
-      <c r="O88" s="103"/>
-      <c r="P88" s="103"/>
-      <c r="Q88" s="103"/>
-      <c r="R88" s="103"/>
-      <c r="S88" s="103"/>
-      <c r="T88" s="103"/>
-      <c r="U88" s="103"/>
-      <c r="V88" s="103"/>
-      <c r="W88" s="103"/>
-      <c r="X88" s="103"/>
-      <c r="Y88" s="103"/>
-      <c r="Z88" s="103"/>
-      <c r="AA88" s="103"/>
+      <c r="E88" s="91"/>
+      <c r="F88" s="91"/>
+      <c r="G88" s="91"/>
+      <c r="H88" s="91"/>
+      <c r="I88" s="91"/>
+      <c r="J88" s="91"/>
+      <c r="K88" s="91"/>
+      <c r="L88" s="91"/>
+      <c r="M88" s="91"/>
+      <c r="N88" s="91"/>
+      <c r="O88" s="91"/>
+      <c r="P88" s="91"/>
+      <c r="Q88" s="91"/>
+      <c r="R88" s="91"/>
+      <c r="S88" s="91"/>
+      <c r="T88" s="91"/>
+      <c r="U88" s="91"/>
+      <c r="V88" s="91"/>
+      <c r="W88" s="91"/>
+      <c r="X88" s="91"/>
+      <c r="Y88" s="91"/>
+      <c r="Z88" s="91"/>
+      <c r="AA88" s="91"/>
     </row>
     <row r="89" spans="3:27">
-      <c r="E89" s="103"/>
-      <c r="F89" s="103"/>
-      <c r="G89" s="103"/>
-      <c r="H89" s="103"/>
-      <c r="I89" s="103"/>
-      <c r="J89" s="103"/>
-      <c r="K89" s="103"/>
-      <c r="L89" s="103"/>
-      <c r="M89" s="103"/>
-      <c r="N89" s="103"/>
-      <c r="O89" s="103"/>
-      <c r="P89" s="103"/>
-      <c r="Q89" s="103"/>
-      <c r="R89" s="103"/>
-      <c r="S89" s="103"/>
-      <c r="T89" s="103"/>
-      <c r="U89" s="103"/>
-      <c r="V89" s="103"/>
-      <c r="W89" s="103"/>
-      <c r="X89" s="103"/>
-      <c r="Y89" s="103"/>
-      <c r="Z89" s="103"/>
-      <c r="AA89" s="103"/>
+      <c r="E89" s="91"/>
+      <c r="F89" s="91"/>
+      <c r="G89" s="91"/>
+      <c r="H89" s="91"/>
+      <c r="I89" s="91"/>
+      <c r="J89" s="91"/>
+      <c r="K89" s="91"/>
+      <c r="L89" s="91"/>
+      <c r="M89" s="91"/>
+      <c r="N89" s="91"/>
+      <c r="O89" s="91"/>
+      <c r="P89" s="91"/>
+      <c r="Q89" s="91"/>
+      <c r="R89" s="91"/>
+      <c r="S89" s="91"/>
+      <c r="T89" s="91"/>
+      <c r="U89" s="91"/>
+      <c r="V89" s="91"/>
+      <c r="W89" s="91"/>
+      <c r="X89" s="91"/>
+      <c r="Y89" s="91"/>
+      <c r="Z89" s="91"/>
+      <c r="AA89" s="91"/>
     </row>
     <row r="90" spans="3:27">
-      <c r="E90" s="103"/>
-      <c r="F90" s="103"/>
-      <c r="G90" s="103"/>
-      <c r="H90" s="103"/>
-      <c r="I90" s="103"/>
-      <c r="J90" s="103"/>
-      <c r="K90" s="103"/>
-      <c r="L90" s="103"/>
-      <c r="M90" s="103"/>
-      <c r="N90" s="103"/>
-      <c r="O90" s="103"/>
-      <c r="P90" s="103"/>
-      <c r="Q90" s="103"/>
-      <c r="R90" s="103"/>
-      <c r="S90" s="103"/>
-      <c r="T90" s="103"/>
-      <c r="U90" s="103"/>
-      <c r="V90" s="103"/>
-      <c r="W90" s="103"/>
-      <c r="X90" s="103"/>
-      <c r="Y90" s="103"/>
-      <c r="Z90" s="103"/>
-      <c r="AA90" s="103"/>
+      <c r="E90" s="91"/>
+      <c r="F90" s="91"/>
+      <c r="G90" s="91"/>
+      <c r="H90" s="91"/>
+      <c r="I90" s="91"/>
+      <c r="J90" s="91"/>
+      <c r="K90" s="91"/>
+      <c r="L90" s="91"/>
+      <c r="M90" s="91"/>
+      <c r="N90" s="91"/>
+      <c r="O90" s="91"/>
+      <c r="P90" s="91"/>
+      <c r="Q90" s="91"/>
+      <c r="R90" s="91"/>
+      <c r="S90" s="91"/>
+      <c r="T90" s="91"/>
+      <c r="U90" s="91"/>
+      <c r="V90" s="91"/>
+      <c r="W90" s="91"/>
+      <c r="X90" s="91"/>
+      <c r="Y90" s="91"/>
+      <c r="Z90" s="91"/>
+      <c r="AA90" s="91"/>
     </row>
     <row r="91" spans="3:27">
-      <c r="E91" s="103"/>
-      <c r="F91" s="103"/>
-      <c r="G91" s="103"/>
-      <c r="H91" s="103"/>
-      <c r="I91" s="103"/>
-      <c r="J91" s="103"/>
-      <c r="K91" s="103"/>
-      <c r="L91" s="103"/>
-      <c r="M91" s="103"/>
-      <c r="N91" s="103"/>
-      <c r="O91" s="103"/>
-      <c r="P91" s="103"/>
-      <c r="Q91" s="103"/>
-      <c r="R91" s="103"/>
-      <c r="S91" s="103"/>
-      <c r="T91" s="103"/>
-      <c r="U91" s="103"/>
-      <c r="V91" s="103"/>
-      <c r="W91" s="103"/>
-      <c r="X91" s="103"/>
-      <c r="Y91" s="103"/>
-      <c r="Z91" s="103"/>
-      <c r="AA91" s="103"/>
+      <c r="E91" s="91"/>
+      <c r="F91" s="91"/>
+      <c r="G91" s="91"/>
+      <c r="H91" s="91"/>
+      <c r="I91" s="91"/>
+      <c r="J91" s="91"/>
+      <c r="K91" s="91"/>
+      <c r="L91" s="91"/>
+      <c r="M91" s="91"/>
+      <c r="N91" s="91"/>
+      <c r="O91" s="91"/>
+      <c r="P91" s="91"/>
+      <c r="Q91" s="91"/>
+      <c r="R91" s="91"/>
+      <c r="S91" s="91"/>
+      <c r="T91" s="91"/>
+      <c r="U91" s="91"/>
+      <c r="V91" s="91"/>
+      <c r="W91" s="91"/>
+      <c r="X91" s="91"/>
+      <c r="Y91" s="91"/>
+      <c r="Z91" s="91"/>
+      <c r="AA91" s="91"/>
     </row>
     <row r="92" spans="3:27">
       <c r="D92" s="1" t="s">
@@ -14064,106 +14063,106 @@
       <c r="AA92" s="45"/>
     </row>
     <row r="93" spans="3:27">
-      <c r="E93" s="103" t="s">
+      <c r="E93" s="91" t="s">
         <v>1574</v>
       </c>
-      <c r="F93" s="103"/>
-      <c r="G93" s="103"/>
-      <c r="H93" s="103"/>
-      <c r="I93" s="103"/>
-      <c r="J93" s="103"/>
-      <c r="K93" s="103"/>
-      <c r="L93" s="103"/>
-      <c r="M93" s="103"/>
-      <c r="N93" s="103"/>
-      <c r="O93" s="103"/>
-      <c r="P93" s="103"/>
-      <c r="Q93" s="103"/>
-      <c r="R93" s="103"/>
-      <c r="S93" s="103"/>
-      <c r="T93" s="103"/>
-      <c r="U93" s="103"/>
-      <c r="V93" s="103"/>
-      <c r="W93" s="103"/>
-      <c r="X93" s="103"/>
-      <c r="Y93" s="103"/>
-      <c r="Z93" s="103"/>
-      <c r="AA93" s="103"/>
+      <c r="F93" s="91"/>
+      <c r="G93" s="91"/>
+      <c r="H93" s="91"/>
+      <c r="I93" s="91"/>
+      <c r="J93" s="91"/>
+      <c r="K93" s="91"/>
+      <c r="L93" s="91"/>
+      <c r="M93" s="91"/>
+      <c r="N93" s="91"/>
+      <c r="O93" s="91"/>
+      <c r="P93" s="91"/>
+      <c r="Q93" s="91"/>
+      <c r="R93" s="91"/>
+      <c r="S93" s="91"/>
+      <c r="T93" s="91"/>
+      <c r="U93" s="91"/>
+      <c r="V93" s="91"/>
+      <c r="W93" s="91"/>
+      <c r="X93" s="91"/>
+      <c r="Y93" s="91"/>
+      <c r="Z93" s="91"/>
+      <c r="AA93" s="91"/>
     </row>
     <row r="94" spans="3:27">
-      <c r="E94" s="103"/>
-      <c r="F94" s="103"/>
-      <c r="G94" s="103"/>
-      <c r="H94" s="103"/>
-      <c r="I94" s="103"/>
-      <c r="J94" s="103"/>
-      <c r="K94" s="103"/>
-      <c r="L94" s="103"/>
-      <c r="M94" s="103"/>
-      <c r="N94" s="103"/>
-      <c r="O94" s="103"/>
-      <c r="P94" s="103"/>
-      <c r="Q94" s="103"/>
-      <c r="R94" s="103"/>
-      <c r="S94" s="103"/>
-      <c r="T94" s="103"/>
-      <c r="U94" s="103"/>
-      <c r="V94" s="103"/>
-      <c r="W94" s="103"/>
-      <c r="X94" s="103"/>
-      <c r="Y94" s="103"/>
-      <c r="Z94" s="103"/>
-      <c r="AA94" s="103"/>
+      <c r="E94" s="91"/>
+      <c r="F94" s="91"/>
+      <c r="G94" s="91"/>
+      <c r="H94" s="91"/>
+      <c r="I94" s="91"/>
+      <c r="J94" s="91"/>
+      <c r="K94" s="91"/>
+      <c r="L94" s="91"/>
+      <c r="M94" s="91"/>
+      <c r="N94" s="91"/>
+      <c r="O94" s="91"/>
+      <c r="P94" s="91"/>
+      <c r="Q94" s="91"/>
+      <c r="R94" s="91"/>
+      <c r="S94" s="91"/>
+      <c r="T94" s="91"/>
+      <c r="U94" s="91"/>
+      <c r="V94" s="91"/>
+      <c r="W94" s="91"/>
+      <c r="X94" s="91"/>
+      <c r="Y94" s="91"/>
+      <c r="Z94" s="91"/>
+      <c r="AA94" s="91"/>
     </row>
     <row r="95" spans="3:27">
-      <c r="E95" s="103"/>
-      <c r="F95" s="103"/>
-      <c r="G95" s="103"/>
-      <c r="H95" s="103"/>
-      <c r="I95" s="103"/>
-      <c r="J95" s="103"/>
-      <c r="K95" s="103"/>
-      <c r="L95" s="103"/>
-      <c r="M95" s="103"/>
-      <c r="N95" s="103"/>
-      <c r="O95" s="103"/>
-      <c r="P95" s="103"/>
-      <c r="Q95" s="103"/>
-      <c r="R95" s="103"/>
-      <c r="S95" s="103"/>
-      <c r="T95" s="103"/>
-      <c r="U95" s="103"/>
-      <c r="V95" s="103"/>
-      <c r="W95" s="103"/>
-      <c r="X95" s="103"/>
-      <c r="Y95" s="103"/>
-      <c r="Z95" s="103"/>
-      <c r="AA95" s="103"/>
+      <c r="E95" s="91"/>
+      <c r="F95" s="91"/>
+      <c r="G95" s="91"/>
+      <c r="H95" s="91"/>
+      <c r="I95" s="91"/>
+      <c r="J95" s="91"/>
+      <c r="K95" s="91"/>
+      <c r="L95" s="91"/>
+      <c r="M95" s="91"/>
+      <c r="N95" s="91"/>
+      <c r="O95" s="91"/>
+      <c r="P95" s="91"/>
+      <c r="Q95" s="91"/>
+      <c r="R95" s="91"/>
+      <c r="S95" s="91"/>
+      <c r="T95" s="91"/>
+      <c r="U95" s="91"/>
+      <c r="V95" s="91"/>
+      <c r="W95" s="91"/>
+      <c r="X95" s="91"/>
+      <c r="Y95" s="91"/>
+      <c r="Z95" s="91"/>
+      <c r="AA95" s="91"/>
     </row>
     <row r="96" spans="3:27">
-      <c r="E96" s="103"/>
-      <c r="F96" s="103"/>
-      <c r="G96" s="103"/>
-      <c r="H96" s="103"/>
-      <c r="I96" s="103"/>
-      <c r="J96" s="103"/>
-      <c r="K96" s="103"/>
-      <c r="L96" s="103"/>
-      <c r="M96" s="103"/>
-      <c r="N96" s="103"/>
-      <c r="O96" s="103"/>
-      <c r="P96" s="103"/>
-      <c r="Q96" s="103"/>
-      <c r="R96" s="103"/>
-      <c r="S96" s="103"/>
-      <c r="T96" s="103"/>
-      <c r="U96" s="103"/>
-      <c r="V96" s="103"/>
-      <c r="W96" s="103"/>
-      <c r="X96" s="103"/>
-      <c r="Y96" s="103"/>
-      <c r="Z96" s="103"/>
-      <c r="AA96" s="103"/>
+      <c r="E96" s="91"/>
+      <c r="F96" s="91"/>
+      <c r="G96" s="91"/>
+      <c r="H96" s="91"/>
+      <c r="I96" s="91"/>
+      <c r="J96" s="91"/>
+      <c r="K96" s="91"/>
+      <c r="L96" s="91"/>
+      <c r="M96" s="91"/>
+      <c r="N96" s="91"/>
+      <c r="O96" s="91"/>
+      <c r="P96" s="91"/>
+      <c r="Q96" s="91"/>
+      <c r="R96" s="91"/>
+      <c r="S96" s="91"/>
+      <c r="T96" s="91"/>
+      <c r="U96" s="91"/>
+      <c r="V96" s="91"/>
+      <c r="W96" s="91"/>
+      <c r="X96" s="91"/>
+      <c r="Y96" s="91"/>
+      <c r="Z96" s="91"/>
+      <c r="AA96" s="91"/>
     </row>
     <row r="97" spans="1:27">
       <c r="D97" s="1" t="s">
@@ -14171,81 +14170,81 @@
       </c>
     </row>
     <row r="98" spans="1:27">
-      <c r="E98" s="103" t="s">
+      <c r="E98" s="91" t="s">
         <v>1576</v>
       </c>
-      <c r="F98" s="103"/>
-      <c r="G98" s="103"/>
-      <c r="H98" s="103"/>
-      <c r="I98" s="103"/>
-      <c r="J98" s="103"/>
-      <c r="K98" s="103"/>
-      <c r="L98" s="103"/>
-      <c r="M98" s="103"/>
-      <c r="N98" s="103"/>
-      <c r="O98" s="103"/>
-      <c r="P98" s="103"/>
-      <c r="Q98" s="103"/>
-      <c r="R98" s="103"/>
-      <c r="S98" s="103"/>
-      <c r="T98" s="103"/>
-      <c r="U98" s="103"/>
-      <c r="V98" s="103"/>
-      <c r="W98" s="103"/>
-      <c r="X98" s="103"/>
-      <c r="Y98" s="103"/>
-      <c r="Z98" s="103"/>
-      <c r="AA98" s="103"/>
+      <c r="F98" s="91"/>
+      <c r="G98" s="91"/>
+      <c r="H98" s="91"/>
+      <c r="I98" s="91"/>
+      <c r="J98" s="91"/>
+      <c r="K98" s="91"/>
+      <c r="L98" s="91"/>
+      <c r="M98" s="91"/>
+      <c r="N98" s="91"/>
+      <c r="O98" s="91"/>
+      <c r="P98" s="91"/>
+      <c r="Q98" s="91"/>
+      <c r="R98" s="91"/>
+      <c r="S98" s="91"/>
+      <c r="T98" s="91"/>
+      <c r="U98" s="91"/>
+      <c r="V98" s="91"/>
+      <c r="W98" s="91"/>
+      <c r="X98" s="91"/>
+      <c r="Y98" s="91"/>
+      <c r="Z98" s="91"/>
+      <c r="AA98" s="91"/>
     </row>
     <row r="99" spans="1:27">
-      <c r="E99" s="103"/>
-      <c r="F99" s="103"/>
-      <c r="G99" s="103"/>
-      <c r="H99" s="103"/>
-      <c r="I99" s="103"/>
-      <c r="J99" s="103"/>
-      <c r="K99" s="103"/>
-      <c r="L99" s="103"/>
-      <c r="M99" s="103"/>
-      <c r="N99" s="103"/>
-      <c r="O99" s="103"/>
-      <c r="P99" s="103"/>
-      <c r="Q99" s="103"/>
-      <c r="R99" s="103"/>
-      <c r="S99" s="103"/>
-      <c r="T99" s="103"/>
-      <c r="U99" s="103"/>
-      <c r="V99" s="103"/>
-      <c r="W99" s="103"/>
-      <c r="X99" s="103"/>
-      <c r="Y99" s="103"/>
-      <c r="Z99" s="103"/>
-      <c r="AA99" s="103"/>
+      <c r="E99" s="91"/>
+      <c r="F99" s="91"/>
+      <c r="G99" s="91"/>
+      <c r="H99" s="91"/>
+      <c r="I99" s="91"/>
+      <c r="J99" s="91"/>
+      <c r="K99" s="91"/>
+      <c r="L99" s="91"/>
+      <c r="M99" s="91"/>
+      <c r="N99" s="91"/>
+      <c r="O99" s="91"/>
+      <c r="P99" s="91"/>
+      <c r="Q99" s="91"/>
+      <c r="R99" s="91"/>
+      <c r="S99" s="91"/>
+      <c r="T99" s="91"/>
+      <c r="U99" s="91"/>
+      <c r="V99" s="91"/>
+      <c r="W99" s="91"/>
+      <c r="X99" s="91"/>
+      <c r="Y99" s="91"/>
+      <c r="Z99" s="91"/>
+      <c r="AA99" s="91"/>
     </row>
     <row r="100" spans="1:27">
-      <c r="E100" s="103"/>
-      <c r="F100" s="103"/>
-      <c r="G100" s="103"/>
-      <c r="H100" s="103"/>
-      <c r="I100" s="103"/>
-      <c r="J100" s="103"/>
-      <c r="K100" s="103"/>
-      <c r="L100" s="103"/>
-      <c r="M100" s="103"/>
-      <c r="N100" s="103"/>
-      <c r="O100" s="103"/>
-      <c r="P100" s="103"/>
-      <c r="Q100" s="103"/>
-      <c r="R100" s="103"/>
-      <c r="S100" s="103"/>
-      <c r="T100" s="103"/>
-      <c r="U100" s="103"/>
-      <c r="V100" s="103"/>
-      <c r="W100" s="103"/>
-      <c r="X100" s="103"/>
-      <c r="Y100" s="103"/>
-      <c r="Z100" s="103"/>
-      <c r="AA100" s="103"/>
+      <c r="E100" s="91"/>
+      <c r="F100" s="91"/>
+      <c r="G100" s="91"/>
+      <c r="H100" s="91"/>
+      <c r="I100" s="91"/>
+      <c r="J100" s="91"/>
+      <c r="K100" s="91"/>
+      <c r="L100" s="91"/>
+      <c r="M100" s="91"/>
+      <c r="N100" s="91"/>
+      <c r="O100" s="91"/>
+      <c r="P100" s="91"/>
+      <c r="Q100" s="91"/>
+      <c r="R100" s="91"/>
+      <c r="S100" s="91"/>
+      <c r="T100" s="91"/>
+      <c r="U100" s="91"/>
+      <c r="V100" s="91"/>
+      <c r="W100" s="91"/>
+      <c r="X100" s="91"/>
+      <c r="Y100" s="91"/>
+      <c r="Z100" s="91"/>
+      <c r="AA100" s="91"/>
     </row>
     <row r="101" spans="1:27">
       <c r="C101" s="1" t="s">
@@ -14996,21 +14995,21 @@
       <c r="E250" s="79" t="s">
         <v>1725</v>
       </c>
-      <c r="F250" s="104" t="s">
+      <c r="F250" s="92" t="s">
         <v>1738</v>
       </c>
-      <c r="G250" s="104"/>
-      <c r="H250" s="104"/>
-      <c r="I250" s="104"/>
-      <c r="J250" s="104"/>
-      <c r="K250" s="104"/>
-      <c r="L250" s="104"/>
-      <c r="M250" s="104"/>
-      <c r="N250" s="104"/>
-      <c r="O250" s="104"/>
-      <c r="P250" s="104"/>
-      <c r="Q250" s="104"/>
-      <c r="R250" s="105"/>
+      <c r="G250" s="92"/>
+      <c r="H250" s="92"/>
+      <c r="I250" s="92"/>
+      <c r="J250" s="92"/>
+      <c r="K250" s="92"/>
+      <c r="L250" s="92"/>
+      <c r="M250" s="92"/>
+      <c r="N250" s="92"/>
+      <c r="O250" s="92"/>
+      <c r="P250" s="92"/>
+      <c r="Q250" s="92"/>
+      <c r="R250" s="93"/>
     </row>
     <row r="251" spans="2:18" ht="15">
       <c r="B251" s="12" t="s">
@@ -15021,21 +15020,21 @@
       <c r="E251" s="73" t="s">
         <v>1732</v>
       </c>
-      <c r="F251" s="91" t="s">
+      <c r="F251" s="94" t="s">
         <v>1746</v>
       </c>
-      <c r="G251" s="92"/>
-      <c r="H251" s="92"/>
-      <c r="I251" s="92"/>
-      <c r="J251" s="92"/>
-      <c r="K251" s="92"/>
-      <c r="L251" s="92"/>
-      <c r="M251" s="92"/>
-      <c r="N251" s="92"/>
-      <c r="O251" s="92"/>
-      <c r="P251" s="92"/>
-      <c r="Q251" s="92"/>
-      <c r="R251" s="93"/>
+      <c r="G251" s="95"/>
+      <c r="H251" s="95"/>
+      <c r="I251" s="95"/>
+      <c r="J251" s="95"/>
+      <c r="K251" s="95"/>
+      <c r="L251" s="95"/>
+      <c r="M251" s="95"/>
+      <c r="N251" s="95"/>
+      <c r="O251" s="95"/>
+      <c r="P251" s="95"/>
+      <c r="Q251" s="95"/>
+      <c r="R251" s="96"/>
     </row>
     <row r="252" spans="2:18" ht="15">
       <c r="B252" s="12" t="s">
@@ -15046,21 +15045,21 @@
       <c r="E252" s="81" t="s">
         <v>1730</v>
       </c>
-      <c r="F252" s="94" t="s">
+      <c r="F252" s="97" t="s">
         <v>1744</v>
       </c>
-      <c r="G252" s="95"/>
-      <c r="H252" s="95"/>
-      <c r="I252" s="95"/>
-      <c r="J252" s="95"/>
-      <c r="K252" s="95"/>
-      <c r="L252" s="95"/>
-      <c r="M252" s="95"/>
-      <c r="N252" s="95"/>
-      <c r="O252" s="95"/>
-      <c r="P252" s="95"/>
-      <c r="Q252" s="95"/>
-      <c r="R252" s="96"/>
+      <c r="G252" s="98"/>
+      <c r="H252" s="98"/>
+      <c r="I252" s="98"/>
+      <c r="J252" s="98"/>
+      <c r="K252" s="98"/>
+      <c r="L252" s="98"/>
+      <c r="M252" s="98"/>
+      <c r="N252" s="98"/>
+      <c r="O252" s="98"/>
+      <c r="P252" s="98"/>
+      <c r="Q252" s="98"/>
+      <c r="R252" s="99"/>
     </row>
     <row r="253" spans="2:18" ht="15">
       <c r="B253" s="12" t="s">
@@ -15071,21 +15070,21 @@
       <c r="E253" s="73" t="s">
         <v>1731</v>
       </c>
-      <c r="F253" s="91" t="s">
+      <c r="F253" s="94" t="s">
         <v>1747</v>
       </c>
-      <c r="G253" s="92"/>
-      <c r="H253" s="92"/>
-      <c r="I253" s="92"/>
-      <c r="J253" s="92"/>
-      <c r="K253" s="92"/>
-      <c r="L253" s="92"/>
-      <c r="M253" s="92"/>
-      <c r="N253" s="92"/>
-      <c r="O253" s="92"/>
-      <c r="P253" s="92"/>
-      <c r="Q253" s="92"/>
-      <c r="R253" s="93"/>
+      <c r="G253" s="95"/>
+      <c r="H253" s="95"/>
+      <c r="I253" s="95"/>
+      <c r="J253" s="95"/>
+      <c r="K253" s="95"/>
+      <c r="L253" s="95"/>
+      <c r="M253" s="95"/>
+      <c r="N253" s="95"/>
+      <c r="O253" s="95"/>
+      <c r="P253" s="95"/>
+      <c r="Q253" s="95"/>
+      <c r="R253" s="96"/>
     </row>
     <row r="254" spans="2:18" ht="15">
       <c r="B254" s="12" t="s">
@@ -15096,21 +15095,21 @@
       <c r="E254" s="81" t="s">
         <v>1728</v>
       </c>
-      <c r="F254" s="94" t="s">
+      <c r="F254" s="97" t="s">
         <v>1741</v>
       </c>
-      <c r="G254" s="95"/>
-      <c r="H254" s="95"/>
-      <c r="I254" s="95"/>
-      <c r="J254" s="95"/>
-      <c r="K254" s="95"/>
-      <c r="L254" s="95"/>
-      <c r="M254" s="95"/>
-      <c r="N254" s="95"/>
-      <c r="O254" s="95"/>
-      <c r="P254" s="95"/>
-      <c r="Q254" s="95"/>
-      <c r="R254" s="96"/>
+      <c r="G254" s="98"/>
+      <c r="H254" s="98"/>
+      <c r="I254" s="98"/>
+      <c r="J254" s="98"/>
+      <c r="K254" s="98"/>
+      <c r="L254" s="98"/>
+      <c r="M254" s="98"/>
+      <c r="N254" s="98"/>
+      <c r="O254" s="98"/>
+      <c r="P254" s="98"/>
+      <c r="Q254" s="98"/>
+      <c r="R254" s="99"/>
     </row>
     <row r="255" spans="2:18" ht="15">
       <c r="B255" s="12" t="s">
@@ -15121,21 +15120,21 @@
       <c r="E255" s="80" t="s">
         <v>1723</v>
       </c>
-      <c r="F255" s="91" t="s">
+      <c r="F255" s="94" t="s">
         <v>1751</v>
       </c>
-      <c r="G255" s="92"/>
-      <c r="H255" s="92"/>
-      <c r="I255" s="92"/>
-      <c r="J255" s="92"/>
-      <c r="K255" s="92"/>
-      <c r="L255" s="92"/>
-      <c r="M255" s="92"/>
-      <c r="N255" s="92"/>
-      <c r="O255" s="92"/>
-      <c r="P255" s="92"/>
-      <c r="Q255" s="92"/>
-      <c r="R255" s="93"/>
+      <c r="G255" s="95"/>
+      <c r="H255" s="95"/>
+      <c r="I255" s="95"/>
+      <c r="J255" s="95"/>
+      <c r="K255" s="95"/>
+      <c r="L255" s="95"/>
+      <c r="M255" s="95"/>
+      <c r="N255" s="95"/>
+      <c r="O255" s="95"/>
+      <c r="P255" s="95"/>
+      <c r="Q255" s="95"/>
+      <c r="R255" s="96"/>
     </row>
     <row r="256" spans="2:18" ht="15">
       <c r="B256" s="12" t="s">
@@ -15146,21 +15145,21 @@
       <c r="E256" s="81" t="s">
         <v>1723</v>
       </c>
-      <c r="F256" s="94" t="s">
+      <c r="F256" s="97" t="s">
         <v>1740</v>
       </c>
-      <c r="G256" s="95"/>
-      <c r="H256" s="95"/>
-      <c r="I256" s="95"/>
-      <c r="J256" s="95"/>
-      <c r="K256" s="95"/>
-      <c r="L256" s="95"/>
-      <c r="M256" s="95"/>
-      <c r="N256" s="95"/>
-      <c r="O256" s="95"/>
-      <c r="P256" s="95"/>
-      <c r="Q256" s="95"/>
-      <c r="R256" s="96"/>
+      <c r="G256" s="98"/>
+      <c r="H256" s="98"/>
+      <c r="I256" s="98"/>
+      <c r="J256" s="98"/>
+      <c r="K256" s="98"/>
+      <c r="L256" s="98"/>
+      <c r="M256" s="98"/>
+      <c r="N256" s="98"/>
+      <c r="O256" s="98"/>
+      <c r="P256" s="98"/>
+      <c r="Q256" s="98"/>
+      <c r="R256" s="99"/>
     </row>
     <row r="257" spans="2:18" ht="15">
       <c r="B257" s="12" t="s">
@@ -15171,21 +15170,21 @@
       <c r="E257" s="80" t="s">
         <v>1723</v>
       </c>
-      <c r="F257" s="91" t="s">
+      <c r="F257" s="94" t="s">
         <v>1739</v>
       </c>
-      <c r="G257" s="92"/>
-      <c r="H257" s="92"/>
-      <c r="I257" s="92"/>
-      <c r="J257" s="92"/>
-      <c r="K257" s="92"/>
-      <c r="L257" s="92"/>
-      <c r="M257" s="92"/>
-      <c r="N257" s="92"/>
-      <c r="O257" s="92"/>
-      <c r="P257" s="92"/>
-      <c r="Q257" s="92"/>
-      <c r="R257" s="93"/>
+      <c r="G257" s="95"/>
+      <c r="H257" s="95"/>
+      <c r="I257" s="95"/>
+      <c r="J257" s="95"/>
+      <c r="K257" s="95"/>
+      <c r="L257" s="95"/>
+      <c r="M257" s="95"/>
+      <c r="N257" s="95"/>
+      <c r="O257" s="95"/>
+      <c r="P257" s="95"/>
+      <c r="Q257" s="95"/>
+      <c r="R257" s="96"/>
     </row>
     <row r="258" spans="2:18" ht="15">
       <c r="B258" s="12" t="s">
@@ -15196,21 +15195,21 @@
       <c r="E258" s="81" t="s">
         <v>1723</v>
       </c>
-      <c r="F258" s="94" t="s">
+      <c r="F258" s="97" t="s">
         <v>1742</v>
       </c>
-      <c r="G258" s="95"/>
-      <c r="H258" s="95"/>
-      <c r="I258" s="95"/>
-      <c r="J258" s="95"/>
-      <c r="K258" s="95"/>
-      <c r="L258" s="95"/>
-      <c r="M258" s="95"/>
-      <c r="N258" s="95"/>
-      <c r="O258" s="95"/>
-      <c r="P258" s="95"/>
-      <c r="Q258" s="95"/>
-      <c r="R258" s="96"/>
+      <c r="G258" s="98"/>
+      <c r="H258" s="98"/>
+      <c r="I258" s="98"/>
+      <c r="J258" s="98"/>
+      <c r="K258" s="98"/>
+      <c r="L258" s="98"/>
+      <c r="M258" s="98"/>
+      <c r="N258" s="98"/>
+      <c r="O258" s="98"/>
+      <c r="P258" s="98"/>
+      <c r="Q258" s="98"/>
+      <c r="R258" s="99"/>
     </row>
     <row r="259" spans="2:18" ht="15">
       <c r="B259" s="12" t="s">
@@ -15221,21 +15220,21 @@
       <c r="E259" s="80" t="s">
         <v>1723</v>
       </c>
-      <c r="F259" s="91" t="s">
+      <c r="F259" s="94" t="s">
         <v>1745</v>
       </c>
-      <c r="G259" s="92"/>
-      <c r="H259" s="92"/>
-      <c r="I259" s="92"/>
-      <c r="J259" s="92"/>
-      <c r="K259" s="92"/>
-      <c r="L259" s="92"/>
-      <c r="M259" s="92"/>
-      <c r="N259" s="92"/>
-      <c r="O259" s="92"/>
-      <c r="P259" s="92"/>
-      <c r="Q259" s="92"/>
-      <c r="R259" s="93"/>
+      <c r="G259" s="95"/>
+      <c r="H259" s="95"/>
+      <c r="I259" s="95"/>
+      <c r="J259" s="95"/>
+      <c r="K259" s="95"/>
+      <c r="L259" s="95"/>
+      <c r="M259" s="95"/>
+      <c r="N259" s="95"/>
+      <c r="O259" s="95"/>
+      <c r="P259" s="95"/>
+      <c r="Q259" s="95"/>
+      <c r="R259" s="96"/>
     </row>
     <row r="260" spans="2:18" ht="15">
       <c r="B260" s="12" t="s">
@@ -15246,21 +15245,21 @@
       <c r="E260" s="81" t="s">
         <v>1723</v>
       </c>
-      <c r="F260" s="94" t="s">
+      <c r="F260" s="97" t="s">
         <v>1748</v>
       </c>
-      <c r="G260" s="95"/>
-      <c r="H260" s="95"/>
-      <c r="I260" s="95"/>
-      <c r="J260" s="95"/>
-      <c r="K260" s="95"/>
-      <c r="L260" s="95"/>
-      <c r="M260" s="95"/>
-      <c r="N260" s="95"/>
-      <c r="O260" s="95"/>
-      <c r="P260" s="95"/>
-      <c r="Q260" s="95"/>
-      <c r="R260" s="96"/>
+      <c r="G260" s="98"/>
+      <c r="H260" s="98"/>
+      <c r="I260" s="98"/>
+      <c r="J260" s="98"/>
+      <c r="K260" s="98"/>
+      <c r="L260" s="98"/>
+      <c r="M260" s="98"/>
+      <c r="N260" s="98"/>
+      <c r="O260" s="98"/>
+      <c r="P260" s="98"/>
+      <c r="Q260" s="98"/>
+      <c r="R260" s="99"/>
     </row>
     <row r="261" spans="2:18" ht="15">
       <c r="B261" s="12" t="s">
@@ -15271,21 +15270,21 @@
       <c r="E261" s="80" t="s">
         <v>1723</v>
       </c>
-      <c r="F261" s="91" t="s">
+      <c r="F261" s="94" t="s">
         <v>1750</v>
       </c>
-      <c r="G261" s="92"/>
-      <c r="H261" s="92"/>
-      <c r="I261" s="92"/>
-      <c r="J261" s="92"/>
-      <c r="K261" s="92"/>
-      <c r="L261" s="92"/>
-      <c r="M261" s="92"/>
-      <c r="N261" s="92"/>
-      <c r="O261" s="92"/>
-      <c r="P261" s="92"/>
-      <c r="Q261" s="92"/>
-      <c r="R261" s="93"/>
+      <c r="G261" s="95"/>
+      <c r="H261" s="95"/>
+      <c r="I261" s="95"/>
+      <c r="J261" s="95"/>
+      <c r="K261" s="95"/>
+      <c r="L261" s="95"/>
+      <c r="M261" s="95"/>
+      <c r="N261" s="95"/>
+      <c r="O261" s="95"/>
+      <c r="P261" s="95"/>
+      <c r="Q261" s="95"/>
+      <c r="R261" s="96"/>
     </row>
     <row r="262" spans="2:18" ht="15">
       <c r="B262" s="12" t="s">
@@ -15296,97 +15295,97 @@
       <c r="E262" s="81" t="s">
         <v>1723</v>
       </c>
-      <c r="F262" s="100" t="s">
+      <c r="F262" s="103" t="s">
         <v>1753</v>
       </c>
-      <c r="G262" s="101"/>
-      <c r="H262" s="101"/>
-      <c r="I262" s="101"/>
-      <c r="J262" s="101"/>
-      <c r="K262" s="101"/>
-      <c r="L262" s="101"/>
-      <c r="M262" s="101"/>
-      <c r="N262" s="101"/>
-      <c r="O262" s="101"/>
-      <c r="P262" s="101"/>
-      <c r="Q262" s="101"/>
-      <c r="R262" s="102"/>
+      <c r="G262" s="104"/>
+      <c r="H262" s="104"/>
+      <c r="I262" s="104"/>
+      <c r="J262" s="104"/>
+      <c r="K262" s="104"/>
+      <c r="L262" s="104"/>
+      <c r="M262" s="104"/>
+      <c r="N262" s="104"/>
+      <c r="O262" s="104"/>
+      <c r="P262" s="104"/>
+      <c r="Q262" s="104"/>
+      <c r="R262" s="105"/>
     </row>
     <row r="263" spans="2:18" ht="15">
       <c r="B263" s="12"/>
       <c r="C263" s="84"/>
       <c r="D263" s="76"/>
       <c r="E263" s="80"/>
-      <c r="F263" s="91"/>
-      <c r="G263" s="92"/>
-      <c r="H263" s="92"/>
-      <c r="I263" s="92"/>
-      <c r="J263" s="92"/>
-      <c r="K263" s="92"/>
-      <c r="L263" s="92"/>
-      <c r="M263" s="92"/>
-      <c r="N263" s="92"/>
-      <c r="O263" s="92"/>
-      <c r="P263" s="92"/>
-      <c r="Q263" s="92"/>
-      <c r="R263" s="93"/>
+      <c r="F263" s="94"/>
+      <c r="G263" s="95"/>
+      <c r="H263" s="95"/>
+      <c r="I263" s="95"/>
+      <c r="J263" s="95"/>
+      <c r="K263" s="95"/>
+      <c r="L263" s="95"/>
+      <c r="M263" s="95"/>
+      <c r="N263" s="95"/>
+      <c r="O263" s="95"/>
+      <c r="P263" s="95"/>
+      <c r="Q263" s="95"/>
+      <c r="R263" s="96"/>
     </row>
     <row r="264" spans="2:18" ht="15">
       <c r="B264" s="12"/>
       <c r="C264" s="84"/>
       <c r="D264" s="76"/>
       <c r="E264" s="82"/>
-      <c r="F264" s="95"/>
-      <c r="G264" s="95"/>
-      <c r="H264" s="95"/>
-      <c r="I264" s="95"/>
-      <c r="J264" s="95"/>
-      <c r="K264" s="95"/>
-      <c r="L264" s="95"/>
-      <c r="M264" s="95"/>
-      <c r="N264" s="95"/>
-      <c r="O264" s="95"/>
-      <c r="P264" s="95"/>
-      <c r="Q264" s="95"/>
-      <c r="R264" s="96"/>
+      <c r="F264" s="98"/>
+      <c r="G264" s="98"/>
+      <c r="H264" s="98"/>
+      <c r="I264" s="98"/>
+      <c r="J264" s="98"/>
+      <c r="K264" s="98"/>
+      <c r="L264" s="98"/>
+      <c r="M264" s="98"/>
+      <c r="N264" s="98"/>
+      <c r="O264" s="98"/>
+      <c r="P264" s="98"/>
+      <c r="Q264" s="98"/>
+      <c r="R264" s="99"/>
     </row>
     <row r="265" spans="2:18" ht="15">
       <c r="B265" s="12"/>
       <c r="C265" s="84"/>
       <c r="D265" s="76"/>
       <c r="E265" s="80"/>
-      <c r="F265" s="91"/>
-      <c r="G265" s="92"/>
-      <c r="H265" s="92"/>
-      <c r="I265" s="92"/>
-      <c r="J265" s="92"/>
-      <c r="K265" s="92"/>
-      <c r="L265" s="92"/>
-      <c r="M265" s="92"/>
-      <c r="N265" s="92"/>
-      <c r="O265" s="92"/>
-      <c r="P265" s="92"/>
-      <c r="Q265" s="92"/>
-      <c r="R265" s="93"/>
+      <c r="F265" s="94"/>
+      <c r="G265" s="95"/>
+      <c r="H265" s="95"/>
+      <c r="I265" s="95"/>
+      <c r="J265" s="95"/>
+      <c r="K265" s="95"/>
+      <c r="L265" s="95"/>
+      <c r="M265" s="95"/>
+      <c r="N265" s="95"/>
+      <c r="O265" s="95"/>
+      <c r="P265" s="95"/>
+      <c r="Q265" s="95"/>
+      <c r="R265" s="96"/>
     </row>
     <row r="266" spans="2:18" ht="15">
       <c r="B266" s="19"/>
       <c r="C266" s="77"/>
       <c r="D266" s="78"/>
       <c r="E266" s="83"/>
-      <c r="F266" s="97"/>
-      <c r="G266" s="98"/>
-      <c r="H266" s="98"/>
-      <c r="I266" s="98"/>
-      <c r="J266" s="98"/>
-      <c r="K266" s="98"/>
-      <c r="L266" s="98"/>
-      <c r="M266" s="98"/>
-      <c r="N266" s="98"/>
-      <c r="O266" s="98"/>
-      <c r="P266" s="98"/>
-      <c r="Q266" s="98"/>
-      <c r="R266" s="99"/>
+      <c r="F266" s="100"/>
+      <c r="G266" s="101"/>
+      <c r="H266" s="101"/>
+      <c r="I266" s="101"/>
+      <c r="J266" s="101"/>
+      <c r="K266" s="101"/>
+      <c r="L266" s="101"/>
+      <c r="M266" s="101"/>
+      <c r="N266" s="101"/>
+      <c r="O266" s="101"/>
+      <c r="P266" s="101"/>
+      <c r="Q266" s="101"/>
+      <c r="R266" s="102"/>
     </row>
     <row r="267" spans="2:18">
       <c r="B267" s="1" t="s">
@@ -15395,11 +15394,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="E87:AA91"/>
-    <mergeCell ref="E93:AA96"/>
-    <mergeCell ref="B48:P49"/>
-    <mergeCell ref="E98:AA100"/>
-    <mergeCell ref="F250:R250"/>
     <mergeCell ref="F251:R251"/>
     <mergeCell ref="F256:R256"/>
     <mergeCell ref="F258:R258"/>
@@ -15416,6 +15410,11 @@
     <mergeCell ref="F262:R262"/>
     <mergeCell ref="F263:R263"/>
     <mergeCell ref="F264:R264"/>
+    <mergeCell ref="E87:AA91"/>
+    <mergeCell ref="E93:AA96"/>
+    <mergeCell ref="B48:P49"/>
+    <mergeCell ref="E98:AA100"/>
+    <mergeCell ref="F250:R250"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="R20" r:id="rId1" xr:uid="{14375537-5C3D-4253-9650-337AB6789785}"/>
@@ -31651,7 +31650,7 @@
         <v>2.5000000000000356E-3</v>
       </c>
       <c r="M240" s="1">
-        <f t="shared" ref="M240:M271" si="2">_xlfn.NORM.DIST(L240,$K$199,$K$201,FALSE)</f>
+        <f t="shared" ref="M240:M270" si="2">_xlfn.NORM.DIST(L240,$K$199,$K$201,FALSE)</f>
         <v>16.212559423296703</v>
       </c>
     </row>

--- a/WK_Model.xlsx
+++ b/WK_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Technology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B6E2F84-443D-4BCC-A415-0B1F2BF0D80B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F99A00CF-00F7-402E-BB58-623C59987365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="12435" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -5382,13 +5382,13 @@
     <t>(888) 275-3125</t>
   </si>
   <si>
-    <t>11/5/2025</t>
-  </si>
-  <si>
     <t>Q3'25</t>
   </si>
   <si>
     <t xml:space="preserve">Financial Stmts. Notes/Observations </t>
+  </si>
+  <si>
+    <t>1/10/2026</t>
   </si>
 </sst>
 </file>
@@ -6000,15 +6000,6 @@
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -6044,6 +6035,15 @@
     </xf>
     <xf numFmtId="10" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -13274,10 +13274,10 @@
         <v>0</v>
       </c>
       <c r="C5" s="89">
-        <v>88.02</v>
+        <v>89.42</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>1758</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -13288,7 +13288,7 @@
         <v>57.5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -13297,7 +13297,7 @@
       </c>
       <c r="C7" s="90">
         <f>C5*C6</f>
-        <v>5061.1499999999996</v>
+        <v>5141.6500000000005</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -13309,7 +13309,7 @@
         <v>856.79099999999994</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -13321,7 +13321,7 @@
         <v>766.72300000000007</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -13330,7 +13330,7 @@
       </c>
       <c r="C10" s="90">
         <f>C7-C8+C9</f>
-        <v>4971.0819999999994</v>
+        <v>5051.5820000000003</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="15">
@@ -13687,23 +13687,23 @@
       </c>
     </row>
     <row r="48" spans="1:21" ht="14.25" customHeight="1">
-      <c r="B48" s="91" t="s">
+      <c r="B48" s="103" t="s">
         <v>1474</v>
       </c>
-      <c r="C48" s="91"/>
-      <c r="D48" s="91"/>
-      <c r="E48" s="91"/>
-      <c r="F48" s="91"/>
-      <c r="G48" s="91"/>
-      <c r="H48" s="91"/>
-      <c r="I48" s="91"/>
-      <c r="J48" s="91"/>
-      <c r="K48" s="91"/>
-      <c r="L48" s="91"/>
-      <c r="M48" s="91"/>
-      <c r="N48" s="91"/>
-      <c r="O48" s="91"/>
-      <c r="P48" s="91"/>
+      <c r="C48" s="103"/>
+      <c r="D48" s="103"/>
+      <c r="E48" s="103"/>
+      <c r="F48" s="103"/>
+      <c r="G48" s="103"/>
+      <c r="H48" s="103"/>
+      <c r="I48" s="103"/>
+      <c r="J48" s="103"/>
+      <c r="K48" s="103"/>
+      <c r="L48" s="103"/>
+      <c r="M48" s="103"/>
+      <c r="N48" s="103"/>
+      <c r="O48" s="103"/>
+      <c r="P48" s="103"/>
       <c r="Q48" s="45"/>
       <c r="R48" s="60"/>
       <c r="S48" s="60"/>
@@ -13711,21 +13711,21 @@
       <c r="U48" s="60"/>
     </row>
     <row r="49" spans="1:21">
-      <c r="B49" s="91"/>
-      <c r="C49" s="91"/>
-      <c r="D49" s="91"/>
-      <c r="E49" s="91"/>
-      <c r="F49" s="91"/>
-      <c r="G49" s="91"/>
-      <c r="H49" s="91"/>
-      <c r="I49" s="91"/>
-      <c r="J49" s="91"/>
-      <c r="K49" s="91"/>
-      <c r="L49" s="91"/>
-      <c r="M49" s="91"/>
-      <c r="N49" s="91"/>
-      <c r="O49" s="91"/>
-      <c r="P49" s="91"/>
+      <c r="B49" s="103"/>
+      <c r="C49" s="103"/>
+      <c r="D49" s="103"/>
+      <c r="E49" s="103"/>
+      <c r="F49" s="103"/>
+      <c r="G49" s="103"/>
+      <c r="H49" s="103"/>
+      <c r="I49" s="103"/>
+      <c r="J49" s="103"/>
+      <c r="K49" s="103"/>
+      <c r="L49" s="103"/>
+      <c r="M49" s="103"/>
+      <c r="N49" s="103"/>
+      <c r="O49" s="103"/>
+      <c r="P49" s="103"/>
       <c r="Q49" s="45"/>
       <c r="R49" s="60"/>
       <c r="S49" s="60"/>
@@ -13908,131 +13908,131 @@
       </c>
     </row>
     <row r="87" spans="3:27" ht="14.25" customHeight="1">
-      <c r="E87" s="91" t="s">
+      <c r="E87" s="103" t="s">
         <v>1572</v>
       </c>
-      <c r="F87" s="91"/>
-      <c r="G87" s="91"/>
-      <c r="H87" s="91"/>
-      <c r="I87" s="91"/>
-      <c r="J87" s="91"/>
-      <c r="K87" s="91"/>
-      <c r="L87" s="91"/>
-      <c r="M87" s="91"/>
-      <c r="N87" s="91"/>
-      <c r="O87" s="91"/>
-      <c r="P87" s="91"/>
-      <c r="Q87" s="91"/>
-      <c r="R87" s="91"/>
-      <c r="S87" s="91"/>
-      <c r="T87" s="91"/>
-      <c r="U87" s="91"/>
-      <c r="V87" s="91"/>
-      <c r="W87" s="91"/>
-      <c r="X87" s="91"/>
-      <c r="Y87" s="91"/>
-      <c r="Z87" s="91"/>
-      <c r="AA87" s="91"/>
+      <c r="F87" s="103"/>
+      <c r="G87" s="103"/>
+      <c r="H87" s="103"/>
+      <c r="I87" s="103"/>
+      <c r="J87" s="103"/>
+      <c r="K87" s="103"/>
+      <c r="L87" s="103"/>
+      <c r="M87" s="103"/>
+      <c r="N87" s="103"/>
+      <c r="O87" s="103"/>
+      <c r="P87" s="103"/>
+      <c r="Q87" s="103"/>
+      <c r="R87" s="103"/>
+      <c r="S87" s="103"/>
+      <c r="T87" s="103"/>
+      <c r="U87" s="103"/>
+      <c r="V87" s="103"/>
+      <c r="W87" s="103"/>
+      <c r="X87" s="103"/>
+      <c r="Y87" s="103"/>
+      <c r="Z87" s="103"/>
+      <c r="AA87" s="103"/>
     </row>
     <row r="88" spans="3:27">
-      <c r="E88" s="91"/>
-      <c r="F88" s="91"/>
-      <c r="G88" s="91"/>
-      <c r="H88" s="91"/>
-      <c r="I88" s="91"/>
-      <c r="J88" s="91"/>
-      <c r="K88" s="91"/>
-      <c r="L88" s="91"/>
-      <c r="M88" s="91"/>
-      <c r="N88" s="91"/>
-      <c r="O88" s="91"/>
-      <c r="P88" s="91"/>
-      <c r="Q88" s="91"/>
-      <c r="R88" s="91"/>
-      <c r="S88" s="91"/>
-      <c r="T88" s="91"/>
-      <c r="U88" s="91"/>
-      <c r="V88" s="91"/>
-      <c r="W88" s="91"/>
-      <c r="X88" s="91"/>
-      <c r="Y88" s="91"/>
-      <c r="Z88" s="91"/>
-      <c r="AA88" s="91"/>
+      <c r="E88" s="103"/>
+      <c r="F88" s="103"/>
+      <c r="G88" s="103"/>
+      <c r="H88" s="103"/>
+      <c r="I88" s="103"/>
+      <c r="J88" s="103"/>
+      <c r="K88" s="103"/>
+      <c r="L88" s="103"/>
+      <c r="M88" s="103"/>
+      <c r="N88" s="103"/>
+      <c r="O88" s="103"/>
+      <c r="P88" s="103"/>
+      <c r="Q88" s="103"/>
+      <c r="R88" s="103"/>
+      <c r="S88" s="103"/>
+      <c r="T88" s="103"/>
+      <c r="U88" s="103"/>
+      <c r="V88" s="103"/>
+      <c r="W88" s="103"/>
+      <c r="X88" s="103"/>
+      <c r="Y88" s="103"/>
+      <c r="Z88" s="103"/>
+      <c r="AA88" s="103"/>
     </row>
     <row r="89" spans="3:27">
-      <c r="E89" s="91"/>
-      <c r="F89" s="91"/>
-      <c r="G89" s="91"/>
-      <c r="H89" s="91"/>
-      <c r="I89" s="91"/>
-      <c r="J89" s="91"/>
-      <c r="K89" s="91"/>
-      <c r="L89" s="91"/>
-      <c r="M89" s="91"/>
-      <c r="N89" s="91"/>
-      <c r="O89" s="91"/>
-      <c r="P89" s="91"/>
-      <c r="Q89" s="91"/>
-      <c r="R89" s="91"/>
-      <c r="S89" s="91"/>
-      <c r="T89" s="91"/>
-      <c r="U89" s="91"/>
-      <c r="V89" s="91"/>
-      <c r="W89" s="91"/>
-      <c r="X89" s="91"/>
-      <c r="Y89" s="91"/>
-      <c r="Z89" s="91"/>
-      <c r="AA89" s="91"/>
+      <c r="E89" s="103"/>
+      <c r="F89" s="103"/>
+      <c r="G89" s="103"/>
+      <c r="H89" s="103"/>
+      <c r="I89" s="103"/>
+      <c r="J89" s="103"/>
+      <c r="K89" s="103"/>
+      <c r="L89" s="103"/>
+      <c r="M89" s="103"/>
+      <c r="N89" s="103"/>
+      <c r="O89" s="103"/>
+      <c r="P89" s="103"/>
+      <c r="Q89" s="103"/>
+      <c r="R89" s="103"/>
+      <c r="S89" s="103"/>
+      <c r="T89" s="103"/>
+      <c r="U89" s="103"/>
+      <c r="V89" s="103"/>
+      <c r="W89" s="103"/>
+      <c r="X89" s="103"/>
+      <c r="Y89" s="103"/>
+      <c r="Z89" s="103"/>
+      <c r="AA89" s="103"/>
     </row>
     <row r="90" spans="3:27">
-      <c r="E90" s="91"/>
-      <c r="F90" s="91"/>
-      <c r="G90" s="91"/>
-      <c r="H90" s="91"/>
-      <c r="I90" s="91"/>
-      <c r="J90" s="91"/>
-      <c r="K90" s="91"/>
-      <c r="L90" s="91"/>
-      <c r="M90" s="91"/>
-      <c r="N90" s="91"/>
-      <c r="O90" s="91"/>
-      <c r="P90" s="91"/>
-      <c r="Q90" s="91"/>
-      <c r="R90" s="91"/>
-      <c r="S90" s="91"/>
-      <c r="T90" s="91"/>
-      <c r="U90" s="91"/>
-      <c r="V90" s="91"/>
-      <c r="W90" s="91"/>
-      <c r="X90" s="91"/>
-      <c r="Y90" s="91"/>
-      <c r="Z90" s="91"/>
-      <c r="AA90" s="91"/>
+      <c r="E90" s="103"/>
+      <c r="F90" s="103"/>
+      <c r="G90" s="103"/>
+      <c r="H90" s="103"/>
+      <c r="I90" s="103"/>
+      <c r="J90" s="103"/>
+      <c r="K90" s="103"/>
+      <c r="L90" s="103"/>
+      <c r="M90" s="103"/>
+      <c r="N90" s="103"/>
+      <c r="O90" s="103"/>
+      <c r="P90" s="103"/>
+      <c r="Q90" s="103"/>
+      <c r="R90" s="103"/>
+      <c r="S90" s="103"/>
+      <c r="T90" s="103"/>
+      <c r="U90" s="103"/>
+      <c r="V90" s="103"/>
+      <c r="W90" s="103"/>
+      <c r="X90" s="103"/>
+      <c r="Y90" s="103"/>
+      <c r="Z90" s="103"/>
+      <c r="AA90" s="103"/>
     </row>
     <row r="91" spans="3:27">
-      <c r="E91" s="91"/>
-      <c r="F91" s="91"/>
-      <c r="G91" s="91"/>
-      <c r="H91" s="91"/>
-      <c r="I91" s="91"/>
-      <c r="J91" s="91"/>
-      <c r="K91" s="91"/>
-      <c r="L91" s="91"/>
-      <c r="M91" s="91"/>
-      <c r="N91" s="91"/>
-      <c r="O91" s="91"/>
-      <c r="P91" s="91"/>
-      <c r="Q91" s="91"/>
-      <c r="R91" s="91"/>
-      <c r="S91" s="91"/>
-      <c r="T91" s="91"/>
-      <c r="U91" s="91"/>
-      <c r="V91" s="91"/>
-      <c r="W91" s="91"/>
-      <c r="X91" s="91"/>
-      <c r="Y91" s="91"/>
-      <c r="Z91" s="91"/>
-      <c r="AA91" s="91"/>
+      <c r="E91" s="103"/>
+      <c r="F91" s="103"/>
+      <c r="G91" s="103"/>
+      <c r="H91" s="103"/>
+      <c r="I91" s="103"/>
+      <c r="J91" s="103"/>
+      <c r="K91" s="103"/>
+      <c r="L91" s="103"/>
+      <c r="M91" s="103"/>
+      <c r="N91" s="103"/>
+      <c r="O91" s="103"/>
+      <c r="P91" s="103"/>
+      <c r="Q91" s="103"/>
+      <c r="R91" s="103"/>
+      <c r="S91" s="103"/>
+      <c r="T91" s="103"/>
+      <c r="U91" s="103"/>
+      <c r="V91" s="103"/>
+      <c r="W91" s="103"/>
+      <c r="X91" s="103"/>
+      <c r="Y91" s="103"/>
+      <c r="Z91" s="103"/>
+      <c r="AA91" s="103"/>
     </row>
     <row r="92" spans="3:27">
       <c r="D92" s="1" t="s">
@@ -14063,106 +14063,106 @@
       <c r="AA92" s="45"/>
     </row>
     <row r="93" spans="3:27">
-      <c r="E93" s="91" t="s">
+      <c r="E93" s="103" t="s">
         <v>1574</v>
       </c>
-      <c r="F93" s="91"/>
-      <c r="G93" s="91"/>
-      <c r="H93" s="91"/>
-      <c r="I93" s="91"/>
-      <c r="J93" s="91"/>
-      <c r="K93" s="91"/>
-      <c r="L93" s="91"/>
-      <c r="M93" s="91"/>
-      <c r="N93" s="91"/>
-      <c r="O93" s="91"/>
-      <c r="P93" s="91"/>
-      <c r="Q93" s="91"/>
-      <c r="R93" s="91"/>
-      <c r="S93" s="91"/>
-      <c r="T93" s="91"/>
-      <c r="U93" s="91"/>
-      <c r="V93" s="91"/>
-      <c r="W93" s="91"/>
-      <c r="X93" s="91"/>
-      <c r="Y93" s="91"/>
-      <c r="Z93" s="91"/>
-      <c r="AA93" s="91"/>
+      <c r="F93" s="103"/>
+      <c r="G93" s="103"/>
+      <c r="H93" s="103"/>
+      <c r="I93" s="103"/>
+      <c r="J93" s="103"/>
+      <c r="K93" s="103"/>
+      <c r="L93" s="103"/>
+      <c r="M93" s="103"/>
+      <c r="N93" s="103"/>
+      <c r="O93" s="103"/>
+      <c r="P93" s="103"/>
+      <c r="Q93" s="103"/>
+      <c r="R93" s="103"/>
+      <c r="S93" s="103"/>
+      <c r="T93" s="103"/>
+      <c r="U93" s="103"/>
+      <c r="V93" s="103"/>
+      <c r="W93" s="103"/>
+      <c r="X93" s="103"/>
+      <c r="Y93" s="103"/>
+      <c r="Z93" s="103"/>
+      <c r="AA93" s="103"/>
     </row>
     <row r="94" spans="3:27">
-      <c r="E94" s="91"/>
-      <c r="F94" s="91"/>
-      <c r="G94" s="91"/>
-      <c r="H94" s="91"/>
-      <c r="I94" s="91"/>
-      <c r="J94" s="91"/>
-      <c r="K94" s="91"/>
-      <c r="L94" s="91"/>
-      <c r="M94" s="91"/>
-      <c r="N94" s="91"/>
-      <c r="O94" s="91"/>
-      <c r="P94" s="91"/>
-      <c r="Q94" s="91"/>
-      <c r="R94" s="91"/>
-      <c r="S94" s="91"/>
-      <c r="T94" s="91"/>
-      <c r="U94" s="91"/>
-      <c r="V94" s="91"/>
-      <c r="W94" s="91"/>
-      <c r="X94" s="91"/>
-      <c r="Y94" s="91"/>
-      <c r="Z94" s="91"/>
-      <c r="AA94" s="91"/>
+      <c r="E94" s="103"/>
+      <c r="F94" s="103"/>
+      <c r="G94" s="103"/>
+      <c r="H94" s="103"/>
+      <c r="I94" s="103"/>
+      <c r="J94" s="103"/>
+      <c r="K94" s="103"/>
+      <c r="L94" s="103"/>
+      <c r="M94" s="103"/>
+      <c r="N94" s="103"/>
+      <c r="O94" s="103"/>
+      <c r="P94" s="103"/>
+      <c r="Q94" s="103"/>
+      <c r="R94" s="103"/>
+      <c r="S94" s="103"/>
+      <c r="T94" s="103"/>
+      <c r="U94" s="103"/>
+      <c r="V94" s="103"/>
+      <c r="W94" s="103"/>
+      <c r="X94" s="103"/>
+      <c r="Y94" s="103"/>
+      <c r="Z94" s="103"/>
+      <c r="AA94" s="103"/>
     </row>
     <row r="95" spans="3:27">
-      <c r="E95" s="91"/>
-      <c r="F95" s="91"/>
-      <c r="G95" s="91"/>
-      <c r="H95" s="91"/>
-      <c r="I95" s="91"/>
-      <c r="J95" s="91"/>
-      <c r="K95" s="91"/>
-      <c r="L95" s="91"/>
-      <c r="M95" s="91"/>
-      <c r="N95" s="91"/>
-      <c r="O95" s="91"/>
-      <c r="P95" s="91"/>
-      <c r="Q95" s="91"/>
-      <c r="R95" s="91"/>
-      <c r="S95" s="91"/>
-      <c r="T95" s="91"/>
-      <c r="U95" s="91"/>
-      <c r="V95" s="91"/>
-      <c r="W95" s="91"/>
-      <c r="X95" s="91"/>
-      <c r="Y95" s="91"/>
-      <c r="Z95" s="91"/>
-      <c r="AA95" s="91"/>
+      <c r="E95" s="103"/>
+      <c r="F95" s="103"/>
+      <c r="G95" s="103"/>
+      <c r="H95" s="103"/>
+      <c r="I95" s="103"/>
+      <c r="J95" s="103"/>
+      <c r="K95" s="103"/>
+      <c r="L95" s="103"/>
+      <c r="M95" s="103"/>
+      <c r="N95" s="103"/>
+      <c r="O95" s="103"/>
+      <c r="P95" s="103"/>
+      <c r="Q95" s="103"/>
+      <c r="R95" s="103"/>
+      <c r="S95" s="103"/>
+      <c r="T95" s="103"/>
+      <c r="U95" s="103"/>
+      <c r="V95" s="103"/>
+      <c r="W95" s="103"/>
+      <c r="X95" s="103"/>
+      <c r="Y95" s="103"/>
+      <c r="Z95" s="103"/>
+      <c r="AA95" s="103"/>
     </row>
     <row r="96" spans="3:27">
-      <c r="E96" s="91"/>
-      <c r="F96" s="91"/>
-      <c r="G96" s="91"/>
-      <c r="H96" s="91"/>
-      <c r="I96" s="91"/>
-      <c r="J96" s="91"/>
-      <c r="K96" s="91"/>
-      <c r="L96" s="91"/>
-      <c r="M96" s="91"/>
-      <c r="N96" s="91"/>
-      <c r="O96" s="91"/>
-      <c r="P96" s="91"/>
-      <c r="Q96" s="91"/>
-      <c r="R96" s="91"/>
-      <c r="S96" s="91"/>
-      <c r="T96" s="91"/>
-      <c r="U96" s="91"/>
-      <c r="V96" s="91"/>
-      <c r="W96" s="91"/>
-      <c r="X96" s="91"/>
-      <c r="Y96" s="91"/>
-      <c r="Z96" s="91"/>
-      <c r="AA96" s="91"/>
+      <c r="E96" s="103"/>
+      <c r="F96" s="103"/>
+      <c r="G96" s="103"/>
+      <c r="H96" s="103"/>
+      <c r="I96" s="103"/>
+      <c r="J96" s="103"/>
+      <c r="K96" s="103"/>
+      <c r="L96" s="103"/>
+      <c r="M96" s="103"/>
+      <c r="N96" s="103"/>
+      <c r="O96" s="103"/>
+      <c r="P96" s="103"/>
+      <c r="Q96" s="103"/>
+      <c r="R96" s="103"/>
+      <c r="S96" s="103"/>
+      <c r="T96" s="103"/>
+      <c r="U96" s="103"/>
+      <c r="V96" s="103"/>
+      <c r="W96" s="103"/>
+      <c r="X96" s="103"/>
+      <c r="Y96" s="103"/>
+      <c r="Z96" s="103"/>
+      <c r="AA96" s="103"/>
     </row>
     <row r="97" spans="1:27">
       <c r="D97" s="1" t="s">
@@ -14170,81 +14170,81 @@
       </c>
     </row>
     <row r="98" spans="1:27">
-      <c r="E98" s="91" t="s">
+      <c r="E98" s="103" t="s">
         <v>1576</v>
       </c>
-      <c r="F98" s="91"/>
-      <c r="G98" s="91"/>
-      <c r="H98" s="91"/>
-      <c r="I98" s="91"/>
-      <c r="J98" s="91"/>
-      <c r="K98" s="91"/>
-      <c r="L98" s="91"/>
-      <c r="M98" s="91"/>
-      <c r="N98" s="91"/>
-      <c r="O98" s="91"/>
-      <c r="P98" s="91"/>
-      <c r="Q98" s="91"/>
-      <c r="R98" s="91"/>
-      <c r="S98" s="91"/>
-      <c r="T98" s="91"/>
-      <c r="U98" s="91"/>
-      <c r="V98" s="91"/>
-      <c r="W98" s="91"/>
-      <c r="X98" s="91"/>
-      <c r="Y98" s="91"/>
-      <c r="Z98" s="91"/>
-      <c r="AA98" s="91"/>
+      <c r="F98" s="103"/>
+      <c r="G98" s="103"/>
+      <c r="H98" s="103"/>
+      <c r="I98" s="103"/>
+      <c r="J98" s="103"/>
+      <c r="K98" s="103"/>
+      <c r="L98" s="103"/>
+      <c r="M98" s="103"/>
+      <c r="N98" s="103"/>
+      <c r="O98" s="103"/>
+      <c r="P98" s="103"/>
+      <c r="Q98" s="103"/>
+      <c r="R98" s="103"/>
+      <c r="S98" s="103"/>
+      <c r="T98" s="103"/>
+      <c r="U98" s="103"/>
+      <c r="V98" s="103"/>
+      <c r="W98" s="103"/>
+      <c r="X98" s="103"/>
+      <c r="Y98" s="103"/>
+      <c r="Z98" s="103"/>
+      <c r="AA98" s="103"/>
     </row>
     <row r="99" spans="1:27">
-      <c r="E99" s="91"/>
-      <c r="F99" s="91"/>
-      <c r="G99" s="91"/>
-      <c r="H99" s="91"/>
-      <c r="I99" s="91"/>
-      <c r="J99" s="91"/>
-      <c r="K99" s="91"/>
-      <c r="L99" s="91"/>
-      <c r="M99" s="91"/>
-      <c r="N99" s="91"/>
-      <c r="O99" s="91"/>
-      <c r="P99" s="91"/>
-      <c r="Q99" s="91"/>
-      <c r="R99" s="91"/>
-      <c r="S99" s="91"/>
-      <c r="T99" s="91"/>
-      <c r="U99" s="91"/>
-      <c r="V99" s="91"/>
-      <c r="W99" s="91"/>
-      <c r="X99" s="91"/>
-      <c r="Y99" s="91"/>
-      <c r="Z99" s="91"/>
-      <c r="AA99" s="91"/>
+      <c r="E99" s="103"/>
+      <c r="F99" s="103"/>
+      <c r="G99" s="103"/>
+      <c r="H99" s="103"/>
+      <c r="I99" s="103"/>
+      <c r="J99" s="103"/>
+      <c r="K99" s="103"/>
+      <c r="L99" s="103"/>
+      <c r="M99" s="103"/>
+      <c r="N99" s="103"/>
+      <c r="O99" s="103"/>
+      <c r="P99" s="103"/>
+      <c r="Q99" s="103"/>
+      <c r="R99" s="103"/>
+      <c r="S99" s="103"/>
+      <c r="T99" s="103"/>
+      <c r="U99" s="103"/>
+      <c r="V99" s="103"/>
+      <c r="W99" s="103"/>
+      <c r="X99" s="103"/>
+      <c r="Y99" s="103"/>
+      <c r="Z99" s="103"/>
+      <c r="AA99" s="103"/>
     </row>
     <row r="100" spans="1:27">
-      <c r="E100" s="91"/>
-      <c r="F100" s="91"/>
-      <c r="G100" s="91"/>
-      <c r="H100" s="91"/>
-      <c r="I100" s="91"/>
-      <c r="J100" s="91"/>
-      <c r="K100" s="91"/>
-      <c r="L100" s="91"/>
-      <c r="M100" s="91"/>
-      <c r="N100" s="91"/>
-      <c r="O100" s="91"/>
-      <c r="P100" s="91"/>
-      <c r="Q100" s="91"/>
-      <c r="R100" s="91"/>
-      <c r="S100" s="91"/>
-      <c r="T100" s="91"/>
-      <c r="U100" s="91"/>
-      <c r="V100" s="91"/>
-      <c r="W100" s="91"/>
-      <c r="X100" s="91"/>
-      <c r="Y100" s="91"/>
-      <c r="Z100" s="91"/>
-      <c r="AA100" s="91"/>
+      <c r="E100" s="103"/>
+      <c r="F100" s="103"/>
+      <c r="G100" s="103"/>
+      <c r="H100" s="103"/>
+      <c r="I100" s="103"/>
+      <c r="J100" s="103"/>
+      <c r="K100" s="103"/>
+      <c r="L100" s="103"/>
+      <c r="M100" s="103"/>
+      <c r="N100" s="103"/>
+      <c r="O100" s="103"/>
+      <c r="P100" s="103"/>
+      <c r="Q100" s="103"/>
+      <c r="R100" s="103"/>
+      <c r="S100" s="103"/>
+      <c r="T100" s="103"/>
+      <c r="U100" s="103"/>
+      <c r="V100" s="103"/>
+      <c r="W100" s="103"/>
+      <c r="X100" s="103"/>
+      <c r="Y100" s="103"/>
+      <c r="Z100" s="103"/>
+      <c r="AA100" s="103"/>
     </row>
     <row r="101" spans="1:27">
       <c r="C101" s="1" t="s">
@@ -14995,21 +14995,21 @@
       <c r="E250" s="79" t="s">
         <v>1725</v>
       </c>
-      <c r="F250" s="92" t="s">
+      <c r="F250" s="104" t="s">
         <v>1738</v>
       </c>
-      <c r="G250" s="92"/>
-      <c r="H250" s="92"/>
-      <c r="I250" s="92"/>
-      <c r="J250" s="92"/>
-      <c r="K250" s="92"/>
-      <c r="L250" s="92"/>
-      <c r="M250" s="92"/>
-      <c r="N250" s="92"/>
-      <c r="O250" s="92"/>
-      <c r="P250" s="92"/>
-      <c r="Q250" s="92"/>
-      <c r="R250" s="93"/>
+      <c r="G250" s="104"/>
+      <c r="H250" s="104"/>
+      <c r="I250" s="104"/>
+      <c r="J250" s="104"/>
+      <c r="K250" s="104"/>
+      <c r="L250" s="104"/>
+      <c r="M250" s="104"/>
+      <c r="N250" s="104"/>
+      <c r="O250" s="104"/>
+      <c r="P250" s="104"/>
+      <c r="Q250" s="104"/>
+      <c r="R250" s="105"/>
     </row>
     <row r="251" spans="2:18" ht="15">
       <c r="B251" s="12" t="s">
@@ -15020,21 +15020,21 @@
       <c r="E251" s="73" t="s">
         <v>1732</v>
       </c>
-      <c r="F251" s="94" t="s">
+      <c r="F251" s="91" t="s">
         <v>1746</v>
       </c>
-      <c r="G251" s="95"/>
-      <c r="H251" s="95"/>
-      <c r="I251" s="95"/>
-      <c r="J251" s="95"/>
-      <c r="K251" s="95"/>
-      <c r="L251" s="95"/>
-      <c r="M251" s="95"/>
-      <c r="N251" s="95"/>
-      <c r="O251" s="95"/>
-      <c r="P251" s="95"/>
-      <c r="Q251" s="95"/>
-      <c r="R251" s="96"/>
+      <c r="G251" s="92"/>
+      <c r="H251" s="92"/>
+      <c r="I251" s="92"/>
+      <c r="J251" s="92"/>
+      <c r="K251" s="92"/>
+      <c r="L251" s="92"/>
+      <c r="M251" s="92"/>
+      <c r="N251" s="92"/>
+      <c r="O251" s="92"/>
+      <c r="P251" s="92"/>
+      <c r="Q251" s="92"/>
+      <c r="R251" s="93"/>
     </row>
     <row r="252" spans="2:18" ht="15">
       <c r="B252" s="12" t="s">
@@ -15045,21 +15045,21 @@
       <c r="E252" s="81" t="s">
         <v>1730</v>
       </c>
-      <c r="F252" s="97" t="s">
+      <c r="F252" s="94" t="s">
         <v>1744</v>
       </c>
-      <c r="G252" s="98"/>
-      <c r="H252" s="98"/>
-      <c r="I252" s="98"/>
-      <c r="J252" s="98"/>
-      <c r="K252" s="98"/>
-      <c r="L252" s="98"/>
-      <c r="M252" s="98"/>
-      <c r="N252" s="98"/>
-      <c r="O252" s="98"/>
-      <c r="P252" s="98"/>
-      <c r="Q252" s="98"/>
-      <c r="R252" s="99"/>
+      <c r="G252" s="95"/>
+      <c r="H252" s="95"/>
+      <c r="I252" s="95"/>
+      <c r="J252" s="95"/>
+      <c r="K252" s="95"/>
+      <c r="L252" s="95"/>
+      <c r="M252" s="95"/>
+      <c r="N252" s="95"/>
+      <c r="O252" s="95"/>
+      <c r="P252" s="95"/>
+      <c r="Q252" s="95"/>
+      <c r="R252" s="96"/>
     </row>
     <row r="253" spans="2:18" ht="15">
       <c r="B253" s="12" t="s">
@@ -15070,21 +15070,21 @@
       <c r="E253" s="73" t="s">
         <v>1731</v>
       </c>
-      <c r="F253" s="94" t="s">
+      <c r="F253" s="91" t="s">
         <v>1747</v>
       </c>
-      <c r="G253" s="95"/>
-      <c r="H253" s="95"/>
-      <c r="I253" s="95"/>
-      <c r="J253" s="95"/>
-      <c r="K253" s="95"/>
-      <c r="L253" s="95"/>
-      <c r="M253" s="95"/>
-      <c r="N253" s="95"/>
-      <c r="O253" s="95"/>
-      <c r="P253" s="95"/>
-      <c r="Q253" s="95"/>
-      <c r="R253" s="96"/>
+      <c r="G253" s="92"/>
+      <c r="H253" s="92"/>
+      <c r="I253" s="92"/>
+      <c r="J253" s="92"/>
+      <c r="K253" s="92"/>
+      <c r="L253" s="92"/>
+      <c r="M253" s="92"/>
+      <c r="N253" s="92"/>
+      <c r="O253" s="92"/>
+      <c r="P253" s="92"/>
+      <c r="Q253" s="92"/>
+      <c r="R253" s="93"/>
     </row>
     <row r="254" spans="2:18" ht="15">
       <c r="B254" s="12" t="s">
@@ -15095,21 +15095,21 @@
       <c r="E254" s="81" t="s">
         <v>1728</v>
       </c>
-      <c r="F254" s="97" t="s">
+      <c r="F254" s="94" t="s">
         <v>1741</v>
       </c>
-      <c r="G254" s="98"/>
-      <c r="H254" s="98"/>
-      <c r="I254" s="98"/>
-      <c r="J254" s="98"/>
-      <c r="K254" s="98"/>
-      <c r="L254" s="98"/>
-      <c r="M254" s="98"/>
-      <c r="N254" s="98"/>
-      <c r="O254" s="98"/>
-      <c r="P254" s="98"/>
-      <c r="Q254" s="98"/>
-      <c r="R254" s="99"/>
+      <c r="G254" s="95"/>
+      <c r="H254" s="95"/>
+      <c r="I254" s="95"/>
+      <c r="J254" s="95"/>
+      <c r="K254" s="95"/>
+      <c r="L254" s="95"/>
+      <c r="M254" s="95"/>
+      <c r="N254" s="95"/>
+      <c r="O254" s="95"/>
+      <c r="P254" s="95"/>
+      <c r="Q254" s="95"/>
+      <c r="R254" s="96"/>
     </row>
     <row r="255" spans="2:18" ht="15">
       <c r="B255" s="12" t="s">
@@ -15120,21 +15120,21 @@
       <c r="E255" s="80" t="s">
         <v>1723</v>
       </c>
-      <c r="F255" s="94" t="s">
+      <c r="F255" s="91" t="s">
         <v>1751</v>
       </c>
-      <c r="G255" s="95"/>
-      <c r="H255" s="95"/>
-      <c r="I255" s="95"/>
-      <c r="J255" s="95"/>
-      <c r="K255" s="95"/>
-      <c r="L255" s="95"/>
-      <c r="M255" s="95"/>
-      <c r="N255" s="95"/>
-      <c r="O255" s="95"/>
-      <c r="P255" s="95"/>
-      <c r="Q255" s="95"/>
-      <c r="R255" s="96"/>
+      <c r="G255" s="92"/>
+      <c r="H255" s="92"/>
+      <c r="I255" s="92"/>
+      <c r="J255" s="92"/>
+      <c r="K255" s="92"/>
+      <c r="L255" s="92"/>
+      <c r="M255" s="92"/>
+      <c r="N255" s="92"/>
+      <c r="O255" s="92"/>
+      <c r="P255" s="92"/>
+      <c r="Q255" s="92"/>
+      <c r="R255" s="93"/>
     </row>
     <row r="256" spans="2:18" ht="15">
       <c r="B256" s="12" t="s">
@@ -15145,21 +15145,21 @@
       <c r="E256" s="81" t="s">
         <v>1723</v>
       </c>
-      <c r="F256" s="97" t="s">
+      <c r="F256" s="94" t="s">
         <v>1740</v>
       </c>
-      <c r="G256" s="98"/>
-      <c r="H256" s="98"/>
-      <c r="I256" s="98"/>
-      <c r="J256" s="98"/>
-      <c r="K256" s="98"/>
-      <c r="L256" s="98"/>
-      <c r="M256" s="98"/>
-      <c r="N256" s="98"/>
-      <c r="O256" s="98"/>
-      <c r="P256" s="98"/>
-      <c r="Q256" s="98"/>
-      <c r="R256" s="99"/>
+      <c r="G256" s="95"/>
+      <c r="H256" s="95"/>
+      <c r="I256" s="95"/>
+      <c r="J256" s="95"/>
+      <c r="K256" s="95"/>
+      <c r="L256" s="95"/>
+      <c r="M256" s="95"/>
+      <c r="N256" s="95"/>
+      <c r="O256" s="95"/>
+      <c r="P256" s="95"/>
+      <c r="Q256" s="95"/>
+      <c r="R256" s="96"/>
     </row>
     <row r="257" spans="2:18" ht="15">
       <c r="B257" s="12" t="s">
@@ -15170,21 +15170,21 @@
       <c r="E257" s="80" t="s">
         <v>1723</v>
       </c>
-      <c r="F257" s="94" t="s">
+      <c r="F257" s="91" t="s">
         <v>1739</v>
       </c>
-      <c r="G257" s="95"/>
-      <c r="H257" s="95"/>
-      <c r="I257" s="95"/>
-      <c r="J257" s="95"/>
-      <c r="K257" s="95"/>
-      <c r="L257" s="95"/>
-      <c r="M257" s="95"/>
-      <c r="N257" s="95"/>
-      <c r="O257" s="95"/>
-      <c r="P257" s="95"/>
-      <c r="Q257" s="95"/>
-      <c r="R257" s="96"/>
+      <c r="G257" s="92"/>
+      <c r="H257" s="92"/>
+      <c r="I257" s="92"/>
+      <c r="J257" s="92"/>
+      <c r="K257" s="92"/>
+      <c r="L257" s="92"/>
+      <c r="M257" s="92"/>
+      <c r="N257" s="92"/>
+      <c r="O257" s="92"/>
+      <c r="P257" s="92"/>
+      <c r="Q257" s="92"/>
+      <c r="R257" s="93"/>
     </row>
     <row r="258" spans="2:18" ht="15">
       <c r="B258" s="12" t="s">
@@ -15195,21 +15195,21 @@
       <c r="E258" s="81" t="s">
         <v>1723</v>
       </c>
-      <c r="F258" s="97" t="s">
+      <c r="F258" s="94" t="s">
         <v>1742</v>
       </c>
-      <c r="G258" s="98"/>
-      <c r="H258" s="98"/>
-      <c r="I258" s="98"/>
-      <c r="J258" s="98"/>
-      <c r="K258" s="98"/>
-      <c r="L258" s="98"/>
-      <c r="M258" s="98"/>
-      <c r="N258" s="98"/>
-      <c r="O258" s="98"/>
-      <c r="P258" s="98"/>
-      <c r="Q258" s="98"/>
-      <c r="R258" s="99"/>
+      <c r="G258" s="95"/>
+      <c r="H258" s="95"/>
+      <c r="I258" s="95"/>
+      <c r="J258" s="95"/>
+      <c r="K258" s="95"/>
+      <c r="L258" s="95"/>
+      <c r="M258" s="95"/>
+      <c r="N258" s="95"/>
+      <c r="O258" s="95"/>
+      <c r="P258" s="95"/>
+      <c r="Q258" s="95"/>
+      <c r="R258" s="96"/>
     </row>
     <row r="259" spans="2:18" ht="15">
       <c r="B259" s="12" t="s">
@@ -15220,21 +15220,21 @@
       <c r="E259" s="80" t="s">
         <v>1723</v>
       </c>
-      <c r="F259" s="94" t="s">
+      <c r="F259" s="91" t="s">
         <v>1745</v>
       </c>
-      <c r="G259" s="95"/>
-      <c r="H259" s="95"/>
-      <c r="I259" s="95"/>
-      <c r="J259" s="95"/>
-      <c r="K259" s="95"/>
-      <c r="L259" s="95"/>
-      <c r="M259" s="95"/>
-      <c r="N259" s="95"/>
-      <c r="O259" s="95"/>
-      <c r="P259" s="95"/>
-      <c r="Q259" s="95"/>
-      <c r="R259" s="96"/>
+      <c r="G259" s="92"/>
+      <c r="H259" s="92"/>
+      <c r="I259" s="92"/>
+      <c r="J259" s="92"/>
+      <c r="K259" s="92"/>
+      <c r="L259" s="92"/>
+      <c r="M259" s="92"/>
+      <c r="N259" s="92"/>
+      <c r="O259" s="92"/>
+      <c r="P259" s="92"/>
+      <c r="Q259" s="92"/>
+      <c r="R259" s="93"/>
     </row>
     <row r="260" spans="2:18" ht="15">
       <c r="B260" s="12" t="s">
@@ -15245,21 +15245,21 @@
       <c r="E260" s="81" t="s">
         <v>1723</v>
       </c>
-      <c r="F260" s="97" t="s">
+      <c r="F260" s="94" t="s">
         <v>1748</v>
       </c>
-      <c r="G260" s="98"/>
-      <c r="H260" s="98"/>
-      <c r="I260" s="98"/>
-      <c r="J260" s="98"/>
-      <c r="K260" s="98"/>
-      <c r="L260" s="98"/>
-      <c r="M260" s="98"/>
-      <c r="N260" s="98"/>
-      <c r="O260" s="98"/>
-      <c r="P260" s="98"/>
-      <c r="Q260" s="98"/>
-      <c r="R260" s="99"/>
+      <c r="G260" s="95"/>
+      <c r="H260" s="95"/>
+      <c r="I260" s="95"/>
+      <c r="J260" s="95"/>
+      <c r="K260" s="95"/>
+      <c r="L260" s="95"/>
+      <c r="M260" s="95"/>
+      <c r="N260" s="95"/>
+      <c r="O260" s="95"/>
+      <c r="P260" s="95"/>
+      <c r="Q260" s="95"/>
+      <c r="R260" s="96"/>
     </row>
     <row r="261" spans="2:18" ht="15">
       <c r="B261" s="12" t="s">
@@ -15270,21 +15270,21 @@
       <c r="E261" s="80" t="s">
         <v>1723</v>
       </c>
-      <c r="F261" s="94" t="s">
+      <c r="F261" s="91" t="s">
         <v>1750</v>
       </c>
-      <c r="G261" s="95"/>
-      <c r="H261" s="95"/>
-      <c r="I261" s="95"/>
-      <c r="J261" s="95"/>
-      <c r="K261" s="95"/>
-      <c r="L261" s="95"/>
-      <c r="M261" s="95"/>
-      <c r="N261" s="95"/>
-      <c r="O261" s="95"/>
-      <c r="P261" s="95"/>
-      <c r="Q261" s="95"/>
-      <c r="R261" s="96"/>
+      <c r="G261" s="92"/>
+      <c r="H261" s="92"/>
+      <c r="I261" s="92"/>
+      <c r="J261" s="92"/>
+      <c r="K261" s="92"/>
+      <c r="L261" s="92"/>
+      <c r="M261" s="92"/>
+      <c r="N261" s="92"/>
+      <c r="O261" s="92"/>
+      <c r="P261" s="92"/>
+      <c r="Q261" s="92"/>
+      <c r="R261" s="93"/>
     </row>
     <row r="262" spans="2:18" ht="15">
       <c r="B262" s="12" t="s">
@@ -15295,97 +15295,97 @@
       <c r="E262" s="81" t="s">
         <v>1723</v>
       </c>
-      <c r="F262" s="103" t="s">
+      <c r="F262" s="100" t="s">
         <v>1753</v>
       </c>
-      <c r="G262" s="104"/>
-      <c r="H262" s="104"/>
-      <c r="I262" s="104"/>
-      <c r="J262" s="104"/>
-      <c r="K262" s="104"/>
-      <c r="L262" s="104"/>
-      <c r="M262" s="104"/>
-      <c r="N262" s="104"/>
-      <c r="O262" s="104"/>
-      <c r="P262" s="104"/>
-      <c r="Q262" s="104"/>
-      <c r="R262" s="105"/>
+      <c r="G262" s="101"/>
+      <c r="H262" s="101"/>
+      <c r="I262" s="101"/>
+      <c r="J262" s="101"/>
+      <c r="K262" s="101"/>
+      <c r="L262" s="101"/>
+      <c r="M262" s="101"/>
+      <c r="N262" s="101"/>
+      <c r="O262" s="101"/>
+      <c r="P262" s="101"/>
+      <c r="Q262" s="101"/>
+      <c r="R262" s="102"/>
     </row>
     <row r="263" spans="2:18" ht="15">
       <c r="B263" s="12"/>
       <c r="C263" s="84"/>
       <c r="D263" s="76"/>
       <c r="E263" s="80"/>
-      <c r="F263" s="94"/>
-      <c r="G263" s="95"/>
-      <c r="H263" s="95"/>
-      <c r="I263" s="95"/>
-      <c r="J263" s="95"/>
-      <c r="K263" s="95"/>
-      <c r="L263" s="95"/>
-      <c r="M263" s="95"/>
-      <c r="N263" s="95"/>
-      <c r="O263" s="95"/>
-      <c r="P263" s="95"/>
-      <c r="Q263" s="95"/>
-      <c r="R263" s="96"/>
+      <c r="F263" s="91"/>
+      <c r="G263" s="92"/>
+      <c r="H263" s="92"/>
+      <c r="I263" s="92"/>
+      <c r="J263" s="92"/>
+      <c r="K263" s="92"/>
+      <c r="L263" s="92"/>
+      <c r="M263" s="92"/>
+      <c r="N263" s="92"/>
+      <c r="O263" s="92"/>
+      <c r="P263" s="92"/>
+      <c r="Q263" s="92"/>
+      <c r="R263" s="93"/>
     </row>
     <row r="264" spans="2:18" ht="15">
       <c r="B264" s="12"/>
       <c r="C264" s="84"/>
       <c r="D264" s="76"/>
       <c r="E264" s="82"/>
-      <c r="F264" s="98"/>
-      <c r="G264" s="98"/>
-      <c r="H264" s="98"/>
-      <c r="I264" s="98"/>
-      <c r="J264" s="98"/>
-      <c r="K264" s="98"/>
-      <c r="L264" s="98"/>
-      <c r="M264" s="98"/>
-      <c r="N264" s="98"/>
-      <c r="O264" s="98"/>
-      <c r="P264" s="98"/>
-      <c r="Q264" s="98"/>
-      <c r="R264" s="99"/>
+      <c r="F264" s="95"/>
+      <c r="G264" s="95"/>
+      <c r="H264" s="95"/>
+      <c r="I264" s="95"/>
+      <c r="J264" s="95"/>
+      <c r="K264" s="95"/>
+      <c r="L264" s="95"/>
+      <c r="M264" s="95"/>
+      <c r="N264" s="95"/>
+      <c r="O264" s="95"/>
+      <c r="P264" s="95"/>
+      <c r="Q264" s="95"/>
+      <c r="R264" s="96"/>
     </row>
     <row r="265" spans="2:18" ht="15">
       <c r="B265" s="12"/>
       <c r="C265" s="84"/>
       <c r="D265" s="76"/>
       <c r="E265" s="80"/>
-      <c r="F265" s="94"/>
-      <c r="G265" s="95"/>
-      <c r="H265" s="95"/>
-      <c r="I265" s="95"/>
-      <c r="J265" s="95"/>
-      <c r="K265" s="95"/>
-      <c r="L265" s="95"/>
-      <c r="M265" s="95"/>
-      <c r="N265" s="95"/>
-      <c r="O265" s="95"/>
-      <c r="P265" s="95"/>
-      <c r="Q265" s="95"/>
-      <c r="R265" s="96"/>
+      <c r="F265" s="91"/>
+      <c r="G265" s="92"/>
+      <c r="H265" s="92"/>
+      <c r="I265" s="92"/>
+      <c r="J265" s="92"/>
+      <c r="K265" s="92"/>
+      <c r="L265" s="92"/>
+      <c r="M265" s="92"/>
+      <c r="N265" s="92"/>
+      <c r="O265" s="92"/>
+      <c r="P265" s="92"/>
+      <c r="Q265" s="92"/>
+      <c r="R265" s="93"/>
     </row>
     <row r="266" spans="2:18" ht="15">
       <c r="B266" s="19"/>
       <c r="C266" s="77"/>
       <c r="D266" s="78"/>
       <c r="E266" s="83"/>
-      <c r="F266" s="100"/>
-      <c r="G266" s="101"/>
-      <c r="H266" s="101"/>
-      <c r="I266" s="101"/>
-      <c r="J266" s="101"/>
-      <c r="K266" s="101"/>
-      <c r="L266" s="101"/>
-      <c r="M266" s="101"/>
-      <c r="N266" s="101"/>
-      <c r="O266" s="101"/>
-      <c r="P266" s="101"/>
-      <c r="Q266" s="101"/>
-      <c r="R266" s="102"/>
+      <c r="F266" s="97"/>
+      <c r="G266" s="98"/>
+      <c r="H266" s="98"/>
+      <c r="I266" s="98"/>
+      <c r="J266" s="98"/>
+      <c r="K266" s="98"/>
+      <c r="L266" s="98"/>
+      <c r="M266" s="98"/>
+      <c r="N266" s="98"/>
+      <c r="O266" s="98"/>
+      <c r="P266" s="98"/>
+      <c r="Q266" s="98"/>
+      <c r="R266" s="99"/>
     </row>
     <row r="267" spans="2:18">
       <c r="B267" s="1" t="s">
@@ -15394,6 +15394,11 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="E87:AA91"/>
+    <mergeCell ref="E93:AA96"/>
+    <mergeCell ref="B48:P49"/>
+    <mergeCell ref="E98:AA100"/>
+    <mergeCell ref="F250:R250"/>
     <mergeCell ref="F251:R251"/>
     <mergeCell ref="F256:R256"/>
     <mergeCell ref="F258:R258"/>
@@ -15410,11 +15415,6 @@
     <mergeCell ref="F262:R262"/>
     <mergeCell ref="F263:R263"/>
     <mergeCell ref="F264:R264"/>
-    <mergeCell ref="E87:AA91"/>
-    <mergeCell ref="E93:AA96"/>
-    <mergeCell ref="B48:P49"/>
-    <mergeCell ref="E98:AA100"/>
-    <mergeCell ref="F250:R250"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="R20" r:id="rId1" xr:uid="{14375537-5C3D-4253-9650-337AB6789785}"/>
@@ -29236,7 +29236,7 @@
       </c>
       <c r="BX108" s="61">
         <f>Main!C5</f>
-        <v>88.02</v>
+        <v>89.42</v>
       </c>
       <c r="BY108" s="71" t="s">
         <v>1516</v>
@@ -29248,7 +29248,7 @@
       </c>
       <c r="BX109" s="67">
         <f>BX107/BX108-1</f>
-        <v>0.33537069454990953</v>
+        <v>0.31446352644020381</v>
       </c>
       <c r="BY109" s="64" t="str">
         <f>IF(BX109&gt;0,"Upside","Downside")</f>
@@ -29449,7 +29449,7 @@
         <v>13</v>
       </c>
       <c r="AC29" s="2" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="30" spans="8:32" ht="15">
